--- a/Test Scenario/Test Scenario for VWO.xlsx
+++ b/Test Scenario/Test Scenario for VWO.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Case Scenarios" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Test Scenario Template</t>
   </si>
@@ -75,6 +75,60 @@
   </si>
   <si>
     <t>Verify after user reset the password, now verify user should not be able to login with old password.</t>
+  </si>
+  <si>
+    <t>Validate the Login Account functionality</t>
+  </si>
+  <si>
+    <t>Validate the Forget Password  functionality</t>
+  </si>
+  <si>
+    <t>Validate the Change Password functionality</t>
+  </si>
+  <si>
+    <t>Verify the "Remember me" checkbox functionality</t>
+  </si>
+  <si>
+    <t>Verify "Start a free trial" Funtionality</t>
+  </si>
+  <si>
+    <t>Brief Description (EXTRA)</t>
+  </si>
+  <si>
+    <t>(UI) Verify  login field placeholder</t>
+  </si>
+  <si>
+    <t>Checking email and password fields have the placeholder text</t>
+  </si>
+  <si>
+    <t>TS_002</t>
+  </si>
+  <si>
+    <t>TS_003</t>
+  </si>
+  <si>
+    <t>TS_001</t>
+  </si>
+  <si>
+    <t>TS_004</t>
+  </si>
+  <si>
+    <t>TS_005</t>
+  </si>
+  <si>
+    <t>TS_006</t>
+  </si>
+  <si>
+    <t>TS_007</t>
+  </si>
+  <si>
+    <t>(UI) verify "eye" option in password field</t>
+  </si>
+  <si>
+    <t>TS_008</t>
+  </si>
+  <si>
+    <t>Checking password fields have "eye" option for correcting password in all browsers</t>
   </si>
 </sst>
 </file>
@@ -112,7 +166,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,13 +185,68 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B084"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -156,37 +265,65 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
       </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -194,6 +331,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF4B084"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -468,153 +610,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F25"/>
+  <dimension ref="A2:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="99.28515625" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" customWidth="1"/>
+    <col min="3" max="3" width="99.28515625" customWidth="1"/>
+    <col min="4" max="4" width="47.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+    <col min="7" max="7" width="48.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+    </row>
+    <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+    </row>
+    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="C17" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>14</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>